--- a/Result/profitability/2012.xlsx
+++ b/Result/profitability/2012.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.21</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0675</v>
+        <v>0.03999999999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>14.29875</v>
+        <v>14.90375</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.43</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1025</v>
+        <v>0.08125</v>
       </c>
       <c r="N3" t="n">
-        <v>15.49625</v>
+        <v>15.8875</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.59</v>
       </c>
       <c r="M4" t="n">
-        <v>0.16375</v>
+        <v>0.14375</v>
       </c>
       <c r="N4" t="n">
-        <v>16.11875</v>
+        <v>16.5575</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>-0.41</v>
       </c>
       <c r="M5" t="n">
-        <v>0.10125</v>
+        <v>0.08749999999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>14.98</v>
+        <v>15.40625</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.52</v>
       </c>
       <c r="M6" t="n">
-        <v>0.03124999999999999</v>
+        <v>0.007499999999999993</v>
       </c>
       <c r="N6" t="n">
-        <v>14.07125</v>
+        <v>14.78375</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-1.39</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.1575</v>
+        <v>-0.16</v>
       </c>
       <c r="N7" t="n">
-        <v>12.32375</v>
+        <v>12.88125</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>-0.22</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.17875</v>
+        <v>-0.1725</v>
       </c>
       <c r="N8" t="n">
-        <v>12.18125</v>
+        <v>13.01625</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1970</v>
+      </c>
+      <c r="D75" t="n">
+        <v>1615</v>
+      </c>
+      <c r="E75" t="n">
+        <v>355</v>
+      </c>
+      <c r="F75" t="n">
+        <v>18.01</v>
+      </c>
+      <c r="G75" t="n">
+        <v>111</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>5.61%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-52</v>
+      </c>
+      <c r="J75" t="n">
+        <v>59</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-18</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.0325</v>
+      </c>
+      <c r="N75" t="n">
+        <v>14.04375</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.04999999999999999</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.4166666666666666</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>6.680000000000001</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.5895851721094441</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-2.75</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>3.410000000000002</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.2335616438356165</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
